--- a/02_加值成品/八下/八下6-4_三種難度測驗卷.xlsx
+++ b/02_加值成品/八下/八下6-4_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二下學期 八下6-4 液體壓力與浮力　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國二下學期 八下6-4 液體壓力與浮力　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>液體壓力隨深度如何？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>越深越大</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>大氣壓</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>相同</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>各方向相同</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>增加</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>同深度各方向液體壓力？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>上浮</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>相同</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>液體壓力增大</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>大氣壓力</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>各向</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>連通管同液體靜止時液面？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>等高</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>相同</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>向上</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>浮力</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>水平</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>空氣的重量產生？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>越深越大</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>等高</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>上浮</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>大氣壓力</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>大氣壓</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>浸入液體物體受的向上力是？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>浮力</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>大氣壓力</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>液體密度</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>各方向相同</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>向上</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>物體密度小於液體會？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>下沉</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>大氣壓</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>上浮</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>越大</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>浮起</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>浮力的方向是？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>等高</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>向上</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>越深越大</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>各方向相同</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>恆向上</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>水壩底部做較厚因為？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>越深越大</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>向上</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>各方向相同</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>深處壓力大</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>承壓</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>液體越深壓力？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>越大</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>無關</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>大於水</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>液體壓力增大</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>深度</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>物體浸在液體中受到向上的力是？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>浮力</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>液體密度</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>大氣壓力</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>大氣壓力很大</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>向上</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二下學期 八下6-4 液體壓力與浮力　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國二下學期 八下6-4 液體壓力與浮力　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>潛水越深耳朵越痛因為？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>越大</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>液體壓力增大</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>各方向相同</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>大氣壓力</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>深度</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>連通管液面等高與管形狀？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>越深越大</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>無關</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>下沉</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>深處壓力大</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>等高</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>用吸管喝飲料靠什麼？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>相同</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>下沉</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>深處壓力大</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>大氣壓力</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>推入</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>鐵塊沉水中因為密度？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>越深越大</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>無關</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>大於水</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>上浮</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>下沉</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>木頭浮水面因為密度？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>越深越大</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>向上</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>小於水</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>浮力</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>上浮</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>液體壓力還與什麼有關？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>小於水</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>越深越大</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>浮力</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>液體密度</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>密度</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>救生衣增大浮力靠？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>調整水艙進排水改變整體密度</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>同液體液面等高可對照</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>增大排開水體積</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>船體排開大量水產生足夠浮力</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>浮力</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>托里切利實驗測量什麼？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>大氣壓</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>各方向相同</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>相同</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>液體密度</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>實驗</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>物體密度大於液體會？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>越大</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>下沉</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>等高</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>浮力</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>沉</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>連通管內同種液體靜止時液面？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>大氣壓力</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>等高</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>越深越大</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>液體壓力增大</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>水平</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二下學期 八下6-4 液體壓力與浮力　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國二下學期 八下6-4 液體壓力與浮力　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>為何萬噸鋼鐵船能浮在水面？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>船體排開大量水產生足夠浮力</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>吸低壓後大氣壓把飲料壓上來</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>增大排開水體積</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>浮力抵消部分重力</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>浮力</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>水壩設計成下寬上窄的原因？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>同液體液面等高可對照</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>越深液壓越大需更厚承受</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>船體排開大量水產生足夠浮力</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>浮力抵消部分重力</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>液壓</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>用連通管原理如何看遠處水位？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>同液體液面等高可對照</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>增大排開水體積</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>越深液壓越大需更厚承受</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>浮力抵消部分重力</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>應用</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>潛水艇如何控制浮沉？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>調整水艙進排水改變整體密度</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>浮力抵消部分重力</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>吸低壓後大氣壓把飲料壓上來</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>增大排開水體積</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>原理</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>大氣壓能壓扁密閉抽氣罐說明？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>向上</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>大氣壓力很大</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>越深越大</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>大氣壓</t>
         </is>
       </c>
-    </row>
-    <row r="8" ht="34" customHeight="1">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>大氣壓</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>同一深度朝上朝下壓力關係？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>各方向相同</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>越深越大</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>大氣壓力很大</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>液體壓力增大</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>各向同性</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>物體在水中變輕的感覺來自？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>船體排開大量水產生足夠浮力</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>越深液壓越大需更厚承受</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>浮力抵消部分重力</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>增大排開水體積</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>浮力</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>為何國中不算浮力大小？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>船體排開大量水產生足夠浮力</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>調整水艙進排水改變整體密度</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>複雜計算移高中</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>吸低壓後大氣壓把飲料壓上來</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>課綱</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>用大氣壓解釋吸管喝飲料？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>吸低壓後大氣壓把飲料壓上來</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>增大排開水體積</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>浮力抵消部分重力</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>越深液壓越大需更厚承受</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>大氣壓</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>鋼船能浮鐵釘沉的差別？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>船排開水多整體平均密度小</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>增大排開水體積</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>越深液壓越大需更厚承受</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>調整水艙進排水改變整體密度</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>浮力</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/八下/八下6-4_三種難度測驗卷.xlsx
+++ b/02_加值成品/八下/八下6-4_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>增加</t>
+          <t>增加：深度越深，上方壓下來的液體重量越多，液體壓力也越大</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>各向</t>
+          <t>各向：在液體中同一深度處，各個方向所承受的壓力大小都相同，這是液體壓力的重要特性</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>水平</t>
+          <t>水平：同一種液體在互相連通的容器中，靜止時各處液面會保持在同一水平高度</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>大氣壓</t>
+          <t>大氣壓：地球周圍的空氣有重量，這些空氣的重量壓在地表上，就形成了大氣壓力</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>向上</t>
+          <t>向上：物體浸在液體中時，會受到液體給予的一股向上托的力，這股力稱為浮力</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>浮起</t>
+          <t>浮起：當物體密度比液體小時，物體所受的浮力大於重力，物體會浮起</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>恆向上</t>
+          <t>恆向上：浮力是液體對物體施加的托力，方向永遠向上</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>承壓</t>
+          <t>承壓：水深越深液體壓力越大，水壩底部承受的水壓最大，所以要做得比較厚才能承受這麼大的壓力</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>深度</t>
+          <t>深度：液體壓力會隨深度增加而增加，深度越深，上方液體的重量越多，壓力也越大</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>向上</t>
+          <t>向上：物體浸在液體中時，會受到液體給予的一股向上托的力，這股力稱為浮力</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>深度</t>
+          <t>深度：潛水深度越深，上方水的壓力越大，這股增大的液體壓力作用在耳膜上，使耳朵感到疼痛</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>等高</t>
+          <t>等高：不論連通管的形狀、粗細如何，只要裝的是同一種液體且處於靜止狀態，各處液面高度都會相同，與管子形狀無關</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>推入</t>
+          <t>推入：吸吸管時管內氣壓降低，外面大氣壓力比管內高，這個壓力差把飲料表面往下壓，使飲料沿著吸管被壓送上來</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>下沉</t>
+          <t>下沉：鐵的密度比水大，物體密度大於液體時，重力大於浮力，所以鐵塊會沉入水中</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>上浮</t>
+          <t>上浮：木頭的密度比水小，物體密度小於液體時，浮力大於重力，所以木頭會浮在水面上</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>密度</t>
+          <t>密度：液體壓力除了和深度有關，也和液體本身的密度有關，密度越大的液體在相同深度產生的壓力越大</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>浮力</t>
+          <t>浮力：救生衣內填充浮力材料，能增加穿著者整體排開水的體積，排開的水越多，受到的浮力就越大</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>實驗</t>
+          <t>實驗：托里切利利用水銀柱實驗，成功測量出大氣壓力的大小，證明大氣確實存在壓力</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>沉</t>
+          <t>沉：當物體的密度比液體大時，物體所受的重力大於浮力，會下沉</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>水平</t>
+          <t>水平：同一種液體在互相連通的容器中，靜止時各處液面會保持在同一水平高度</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>浮力</t>
+          <t>浮力：船身做成中空的形狀，排開的水量很多，產生的浮力足以支撐整艘船(含內部空氣)的重量，即使鋼鐵本身密度比水大，整艘船能浮起</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>液壓</t>
+          <t>液壓：水深越深液體壓力越大，水壩底部承受的水壓遠大於上方，所以底部要設計得更寬厚，才能承受住深處強大的水壓</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>應用</t>
+          <t>應用：利用連通管中同一液體靜止時液面等高的原理，可以透過觀察連接管一端透明管內的液面高度，間接對照出遠處另一端(看不到)水位的高低</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>原理</t>
+          <t>原理：潛水艇利用水艙注水或排水，改變艇身整體的平均密度：注水使密度變大於海水而下沉，排水使密度變小於海水而上浮</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>大氣壓</t>
+          <t>大氣壓：密閉容器內的空氣被抽走後，內部壓力大幅降低，外部大氣壓力遠大於內部壓力，這個壓力差足以把罐子壓扁，證明大氣壓力其實非常大</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>各向同性</t>
+          <t>各向同性：液體中同一深度處，不論朝上、朝下或側面，各個方向所承受的壓力大小都相同，這是液體壓力各向同性的特性</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>浮力</t>
+          <t>浮力：物體浸在水中會受到向上的浮力，這股浮力抵消了一部分重力，讓人感覺物體在水中變輕了</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>課綱</t>
+          <t>課綱：浮力大小的精確計算(阿基米德原理的定量應用)涉及較複雜的數學運算，依照課綱安排移到高中階段才深入學習，國中只需理解浮力的定性概念</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>大氣壓</t>
+          <t>大氣壓：用嘴吸吸管時，管內的氣壓降低，外面大氣壓力比管內高，這個壓力差把飲料表面往下壓，使飲料沿著吸管被壓送上來，並不是嘴巴把飲料「吸」上來的</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>浮力</t>
+          <t>浮力：鋼船雖然是金屬做的，但做成中空的船身形狀，排開的水量很多，使整艘船（含內部空氣）的平均密度小於水，所受浮力大於重力所以能浮；鐵釘是實心的，平均密度比水大，所以會下沉</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/八下/八下6-4_三種難度測驗卷.xlsx
+++ b/02_加值成品/八下/八下6-4_三種難度測驗卷.xlsx
@@ -568,17 +568,17 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>大氣壓</t>
+          <t>上浮</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>相同</t>
+          <t>大氣壓力</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>各方向相同</t>
+          <t>大氣壓力很大</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -603,7 +603,7 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>上浮</t>
+          <t>無關</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
@@ -613,12 +613,12 @@
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>液體壓力增大</t>
+          <t>越大</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>大氣壓力</t>
+          <t>向上</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>上浮</t>
+          <t>液體壓力增大</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -888,17 +888,17 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>無關</t>
+          <t>大氣壓力</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>大於水</t>
+          <t>向上</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>液體壓力增大</t>
+          <t>上浮</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1119,17 +1119,17 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>相同</t>
+          <t>等高</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>下沉</t>
+          <t>無關</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>深處壓力大</t>
+          <t>大於水</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -1324,17 +1324,17 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>各方向相同</t>
+          <t>向上</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>相同</t>
+          <t>深處壓力大</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>液體密度</t>
+          <t>大於水</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>向上</t>
+          <t>液體密度</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -1685,12 +1685,12 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>越深越大</t>
+          <t>等高</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>大氣壓</t>
+          <t>相同</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -1720,12 +1720,12 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>越深越大</t>
+          <t>上浮</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>大氣壓力很大</t>
+          <t>大氣壓力</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
